--- a/No of Brokers and No of accounts.xlsx
+++ b/No of Brokers and No of accounts.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{D906692C-4C0C-42DA-9D5A-5A05C5F06D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12591471-01DC-4EBE-9C5F-DAFDC5CCB137}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{D906692C-4C0C-42DA-9D5A-5A05C5F06D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3E38AAD-66CF-4FB6-8E63-F0707D2C9B79}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2956C8BA-FF58-41B4-A634-4B0CF0C0799C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2956C8BA-FF58-41B4-A634-4B0CF0C0799C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="167">
   <si>
     <t>Alberto Pasini</t>
   </si>
@@ -496,6 +497,54 @@
   </si>
   <si>
     <t>Others(please specify)</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>terminalogy</t>
+  </si>
+  <si>
+    <t>BBg</t>
+  </si>
+  <si>
+    <t>ticker</t>
+  </si>
+  <si>
+    <t>RICCode</t>
+  </si>
+  <si>
+    <t>Reuters</t>
+  </si>
+  <si>
+    <t>0005.HK</t>
+  </si>
+  <si>
+    <t>5 HK</t>
+  </si>
+  <si>
+    <t>xxxxx</t>
+  </si>
+  <si>
+    <t>jacob to osin</t>
+  </si>
+  <si>
+    <t>from isn go to settings table</t>
+  </si>
+  <si>
+    <t>then setting to gopdf</t>
+  </si>
+  <si>
+    <t>xzccxzcvxz</t>
+  </si>
+  <si>
+    <t>AAPL US</t>
+  </si>
+  <si>
+    <t>Ric code</t>
   </si>
 </sst>
 </file>
@@ -620,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -662,6 +711,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3602,7 +3654,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="19" t="s">
         <v>69</v>
       </c>
       <c r="B23" s="15">
@@ -4186,4 +4238,85 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B4DA24-183C-4464-9780-B2192AD5383F}">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L13" t="s">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s">
+        <v>151</v>
+      </c>
+      <c r="N13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L14" t="s">
+        <v>159</v>
+      </c>
+      <c r="M14" t="s">
+        <v>154</v>
+      </c>
+      <c r="N14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>158</v>
+      </c>
+      <c r="M15" t="s">
+        <v>156</v>
+      </c>
+      <c r="N15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>